--- a/static/migration_templates/04_members.xlsx
+++ b/static/migration_templates/04_members.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="members" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="_instructions" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="members" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="_instructions" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -430,7 +430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I2"/>
+  <dimension ref="A1:AA2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -442,6 +442,24 @@
     <col width="18" customWidth="1" min="7" max="7"/>
     <col width="18" customWidth="1" min="8" max="8"/>
     <col width="18" customWidth="1" min="9" max="9"/>
+    <col width="18" customWidth="1" min="10" max="10"/>
+    <col width="18" customWidth="1" min="11" max="11"/>
+    <col width="18" customWidth="1" min="12" max="12"/>
+    <col width="18" customWidth="1" min="13" max="13"/>
+    <col width="18" customWidth="1" min="14" max="14"/>
+    <col width="18" customWidth="1" min="15" max="15"/>
+    <col width="18" customWidth="1" min="16" max="16"/>
+    <col width="18" customWidth="1" min="17" max="17"/>
+    <col width="18" customWidth="1" min="18" max="18"/>
+    <col width="18" customWidth="1" min="19" max="19"/>
+    <col width="18" customWidth="1" min="20" max="20"/>
+    <col width="18" customWidth="1" min="21" max="21"/>
+    <col width="18" customWidth="1" min="22" max="22"/>
+    <col width="18" customWidth="1" min="23" max="23"/>
+    <col width="18" customWidth="1" min="24" max="24"/>
+    <col width="18" customWidth="1" min="25" max="25"/>
+    <col width="18" customWidth="1" min="26" max="26"/>
+    <col width="18" customWidth="1" min="27" max="27"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -452,42 +470,132 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>full_name</t>
+          <t>last_name</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
+          <t>first_name</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>middle_name</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>tin</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>membership_date</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>bod_acceptance_resolution</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>membership_type</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>initial_shares</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>initial_subscription_amount</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>initial_paid_up_capital</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>address</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>birth_date</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>gender</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>civil_status</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>highest_education</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>occupation_income_source</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>number_of_dependents</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>religion_social_affiliation</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>annual_income</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>register_entry_date</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
           <t>email</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>phone</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>address</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>membership_date</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>share_capital</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>savings_balance</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>status</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>termination_date</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>termination_bod_resolution</t>
         </is>
       </c>
     </row>
@@ -499,44 +607,126 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Maria Santos</t>
+          <t>Santos</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
+          <t>Maria</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>123-456-789-000</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>2024-01-15</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>BOD-2024-01</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Regular</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>5000</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>5000</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>123 Main St, Quezon City</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>1990-05-20</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>Single</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>College</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>Teacher</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>Roman Catholic</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>360000</t>
+        </is>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>2024-01-15</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
           <t>maria@email.com</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t>09171234567</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>Quezon City</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>2024-01-15</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>5000</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
+      <c r="X2" t="inlineStr">
         <is>
           <t>2500</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="Y2" t="inlineStr">
         <is>
           <t>Active</t>
         </is>
       </c>
+      <c r="Z2" t="inlineStr"/>
+      <c r="AA2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -549,7 +739,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A9"/>
+  <dimension ref="A1:A19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -562,35 +752,91 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Description</t>
+          <t>PostgreSQL table</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Member registry. membership_date format: YYYY-MM-DD. status: Active or Inactive.</t>
+          <t>members</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Required columns</t>
+          <t>Description</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>member_no, full_name</t>
+          <t>CDA MC 2012-16 membership registry (members table). membership_date = date accepted (I-a). initial_paid_up_capital sets share_capital on import; optional savings_balance creates opening member ledger entries. full_name is computed from name parts. Dates: YYYY-MM-DD. status: Active, Inactive, or Terminated.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>Required columns</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>member_no, last_name, first_name, tin, membership_date</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
           <t>Paste your data starting row 2 on the main sheet. Do not rename header row.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Valid values</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>membership_type: Regular, Associate, Institutional, Honorary</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>gender: Male, Female</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>civil_status: Single, Married, Widowed, Separated, Divorced</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>highest_education: Elementary, High School, Vocational, College, Post Graduate, Doctorate</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>status: Active, Inactive, Terminated</t>
         </is>
       </c>
     </row>

--- a/static/migration_templates/04_members.xlsx
+++ b/static/migration_templates/04_members.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="members" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="_instructions" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="members" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="_instructions" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
